--- a/Kabakibi_Ex3A_tables.xlsx
+++ b/Kabakibi_Ex3A_tables.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Owner" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>owner_id</t>
   </si>
@@ -94,16 +94,69 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>Havanese</t>
+  </si>
+  <si>
+    <t>11 lbs (Small)</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>https://t3.ftcdn.net/jpg/03/58/32/92/360_F_358329259_MWxTVvYonW8L1qxUgNn90uWN4Yh0atZn.jpg</t>
+  </si>
+  <si>
+    <t>2 Years</t>
+  </si>
+  <si>
+    <t>Steve</t>
+  </si>
+  <si>
+    <t>Mary Smith, 5550198888</t>
+  </si>
+  <si>
+    <t>09:00 AM - 10:00 AM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1012</t>
+  </si>
+  <si>
+    <t>Fresh water provided after the walk. Locked the back door.</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>521 street ave, Newark NJ 07102</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -138,15 +191,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -425,10 +482,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -445,6 +503,20 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>2223334444</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -452,11 +524,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -485,14 +558,43 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
@@ -513,6 +615,20 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>2224445555</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -520,12 +636,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -551,19 +668,46 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1012</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>402</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46130</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -586,6 +730,26 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5001</v>
+      </c>
+      <c r="B2">
+        <v>1012</v>
+      </c>
+      <c r="C2">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46130</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Kabakibi_Ex3A_tables.xlsx
+++ b/Kabakibi_Ex3A_tables.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350"/>
   </bookViews>
   <sheets>
     <sheet name="Owner" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="151">
   <si>
     <t>owner_id</t>
   </si>
@@ -139,6 +139,348 @@
   </si>
   <si>
     <t>521 street ave, Newark NJ 07102</t>
+  </si>
+  <si>
+    <t>Mike Johnson</t>
+  </si>
+  <si>
+    <t>12 Market St, Camden NJ 08102</t>
+  </si>
+  <si>
+    <t>Sara Lee</t>
+  </si>
+  <si>
+    <t>89 Broad St, Newark NJ 07104</t>
+  </si>
+  <si>
+    <t>David Kim</t>
+  </si>
+  <si>
+    <t>45 Park Ave, Jersey City NJ 07302</t>
+  </si>
+  <si>
+    <t>Emily Clark</t>
+  </si>
+  <si>
+    <t>77 River Rd, Hoboken NJ 07030</t>
+  </si>
+  <si>
+    <t>Chris Brown</t>
+  </si>
+  <si>
+    <t>101 Main St, Trenton NJ 08608</t>
+  </si>
+  <si>
+    <t>Olivia White</t>
+  </si>
+  <si>
+    <t>22 Elm St, Cherry Hill NJ 08002</t>
+  </si>
+  <si>
+    <t>James Green</t>
+  </si>
+  <si>
+    <t>9 Pine St, Camden NJ 08103</t>
+  </si>
+  <si>
+    <t>Sophia Adams</t>
+  </si>
+  <si>
+    <t>55 Oak St, Newark NJ 07105</t>
+  </si>
+  <si>
+    <t>Daniel Hall</t>
+  </si>
+  <si>
+    <t>88 Maple Ave, Paterson NJ 07501</t>
+  </si>
+  <si>
+    <t>Liam Scott</t>
+  </si>
+  <si>
+    <t>33 Cedar Rd, Edison NJ 08817</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Labrador</t>
+  </si>
+  <si>
+    <t>55 lbs (Large)</t>
+  </si>
+  <si>
+    <t>https://example.com/dog2.jpg</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>Poodle</t>
+  </si>
+  <si>
+    <t>20 lbs (Medium)</t>
+  </si>
+  <si>
+    <t>Allergy</t>
+  </si>
+  <si>
+    <t>https://example.com/dog3.jpg</t>
+  </si>
+  <si>
+    <t>Rocky</t>
+  </si>
+  <si>
+    <t>Bulldog</t>
+  </si>
+  <si>
+    <t>50 lbs (Large)</t>
+  </si>
+  <si>
+    <t>Breathing issues</t>
+  </si>
+  <si>
+    <t>https://example.com/dog4.jpg</t>
+  </si>
+  <si>
+    <t>Milo</t>
+  </si>
+  <si>
+    <t>Beagle</t>
+  </si>
+  <si>
+    <t>25 lbs (Medium)</t>
+  </si>
+  <si>
+    <t>https://example.com/dog5.jpg</t>
+  </si>
+  <si>
+    <t>Coco</t>
+  </si>
+  <si>
+    <t>Chihuahua</t>
+  </si>
+  <si>
+    <t>8 lbs (Small)</t>
+  </si>
+  <si>
+    <t>https://example.com/dog6.jpg</t>
+  </si>
+  <si>
+    <t>Buddy</t>
+  </si>
+  <si>
+    <t>Golden Retriever</t>
+  </si>
+  <si>
+    <t>60 lbs (Large)</t>
+  </si>
+  <si>
+    <t>Hip pain</t>
+  </si>
+  <si>
+    <t>https://example.com/dog7.jpg</t>
+  </si>
+  <si>
+    <t>Daisy</t>
+  </si>
+  <si>
+    <t>Shih Tzu</t>
+  </si>
+  <si>
+    <t>12 lbs (Small)</t>
+  </si>
+  <si>
+    <t>https://example.com/dog8.jpg</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>Boxer</t>
+  </si>
+  <si>
+    <t>65 lbs (Large)</t>
+  </si>
+  <si>
+    <t>https://example.com/dog9.jpg</t>
+  </si>
+  <si>
+    <t>Lucy</t>
+  </si>
+  <si>
+    <t>Corgi</t>
+  </si>
+  <si>
+    <t>28 lbs (Medium)</t>
+  </si>
+  <si>
+    <t>https://example.com/dog10.jpg</t>
+  </si>
+  <si>
+    <t>Bailey</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>https://example.com/dog11.jpg</t>
+  </si>
+  <si>
+    <t>Anna Lee</t>
+  </si>
+  <si>
+    <t>John Lee, 5550001111</t>
+  </si>
+  <si>
+    <t>Mark Davis</t>
+  </si>
+  <si>
+    <t>Lisa Davis, 5550002222</t>
+  </si>
+  <si>
+    <t>Nina Patel</t>
+  </si>
+  <si>
+    <t>Raj Patel, 5550003333</t>
+  </si>
+  <si>
+    <t>Tom Wilson</t>
+  </si>
+  <si>
+    <t>Sarah Wilson, 5550004444</t>
+  </si>
+  <si>
+    <t>Eva Martinez</t>
+  </si>
+  <si>
+    <t>Carlos Martinez, 5550005555</t>
+  </si>
+  <si>
+    <t>Ryan Moore</t>
+  </si>
+  <si>
+    <t>Emma Moore, 5550006666</t>
+  </si>
+  <si>
+    <t>Chloe King</t>
+  </si>
+  <si>
+    <t>James King, 5550007777</t>
+  </si>
+  <si>
+    <t>Noah Wright</t>
+  </si>
+  <si>
+    <t>Mia Wright, 5550008888</t>
+  </si>
+  <si>
+    <t>Ava Lopez</t>
+  </si>
+  <si>
+    <t>Luis Lopez, 5550009999</t>
+  </si>
+  <si>
+    <t>Ethan Young</t>
+  </si>
+  <si>
+    <t>Olivia Young, 5550010000</t>
+  </si>
+  <si>
+    <t>10:00 AM - 11:00 AM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1013</t>
+  </si>
+  <si>
+    <t>Dog was energetic.</t>
+  </si>
+  <si>
+    <t>11:00 AM - 12:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1014</t>
+  </si>
+  <si>
+    <t>Avoided other dogs.</t>
+  </si>
+  <si>
+    <t>12:00 PM - 01:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1015</t>
+  </si>
+  <si>
+    <t>Short walk due to heat.</t>
+  </si>
+  <si>
+    <t>01:00 PM - 02:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1016</t>
+  </si>
+  <si>
+    <t>Very calm behavior.</t>
+  </si>
+  <si>
+    <t>02:00 PM - 03:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1017</t>
+  </si>
+  <si>
+    <t>Drank water well.</t>
+  </si>
+  <si>
+    <t>03:00 PM - 04:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1018</t>
+  </si>
+  <si>
+    <t>Slow walking due to hip.</t>
+  </si>
+  <si>
+    <t>04:00 PM - 05:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1019</t>
+  </si>
+  <si>
+    <t>Playful and active.</t>
+  </si>
+  <si>
+    <t>05:00 PM - 06:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1020</t>
+  </si>
+  <si>
+    <t>No issues.</t>
+  </si>
+  <si>
+    <t>06:00 PM - 07:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1021</t>
+  </si>
+  <si>
+    <t>Good behavior.</t>
+  </si>
+  <si>
+    <t>07:00 PM - 08:00 PM</t>
+  </si>
+  <si>
+    <t>https://maps.walktrack.com/path/1022</t>
+  </si>
+  <si>
+    <t>Very energetic.</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Debit Card</t>
   </si>
 </sst>
 </file>
@@ -177,7 +519,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -198,9 +540,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -482,11 +824,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -515,6 +858,146 @@
       </c>
       <c r="D2" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3">
+        <v>2221113333</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>2225557777</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5">
+        <v>2228889999</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6">
+        <v>2226664444</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7">
+        <v>2229992222</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>2227773333</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9">
+        <v>2224441111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>2223338888</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11">
+        <v>2222226666</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12">
+        <v>2221119999</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -524,11 +1007,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -536,7 +1019,7 @@
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
@@ -580,8 +1063,268 @@
       <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>111</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -594,11 +1337,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -627,6 +1371,146 @@
       </c>
       <c r="D2" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>403</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3">
+        <v>2221012020</v>
+      </c>
+      <c r="D3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>404</v>
+      </c>
+      <c r="B4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>2222023030</v>
+      </c>
+      <c r="D4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>405</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5">
+        <v>2223034040</v>
+      </c>
+      <c r="D5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>406</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6">
+        <v>2224045050</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>407</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7">
+        <v>2225056060</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>408</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8">
+        <v>2226067070</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>409</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>2227078080</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>410</v>
+      </c>
+      <c r="B10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10">
+        <v>2228089090</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>411</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11">
+        <v>2229091010</v>
+      </c>
+      <c r="D11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>412</v>
+      </c>
+      <c r="B12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12">
+        <v>2220102020</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -636,23 +1520,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D1" t="s">
@@ -678,17 +1563,247 @@
       <c r="C2">
         <v>402</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>46130</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G2" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1013</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>403</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1014</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>404</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1015</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>405</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1016</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>406</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1017</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>407</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1018</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>408</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1019</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>409</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1020</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>410</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1021</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>411</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1022</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>412</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46130</v>
+      </c>
+      <c r="E12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -701,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
@@ -714,7 +1829,7 @@
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" t="s">
@@ -743,10 +1858,210 @@
       <c r="D2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>46130</v>
       </c>
       <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5002</v>
+      </c>
+      <c r="B3">
+        <v>1013</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>5003</v>
+      </c>
+      <c r="B4">
+        <v>1014</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>5004</v>
+      </c>
+      <c r="B5">
+        <v>1015</v>
+      </c>
+      <c r="C5">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5005</v>
+      </c>
+      <c r="B6">
+        <v>1016</v>
+      </c>
+      <c r="C6">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5006</v>
+      </c>
+      <c r="B7">
+        <v>1017</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5007</v>
+      </c>
+      <c r="B8">
+        <v>1018</v>
+      </c>
+      <c r="C8">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>5008</v>
+      </c>
+      <c r="B9">
+        <v>1019</v>
+      </c>
+      <c r="C9">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5009</v>
+      </c>
+      <c r="B10">
+        <v>1020</v>
+      </c>
+      <c r="C10">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>5010</v>
+      </c>
+      <c r="B11">
+        <v>1021</v>
+      </c>
+      <c r="C11">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>5011</v>
+      </c>
+      <c r="B12">
+        <v>1022</v>
+      </c>
+      <c r="C12">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F12" t="s">
         <v>35</v>
       </c>
     </row>
